--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488139_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488139_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8702</v>
+        <v>4.3128</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1782</v>
+        <v>6.6453</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3079</v>
+        <v>-2.3325</v>
       </c>
       <c r="G2" t="n">
         <v>0.0371</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1587</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2896</v>
+        <v>0.7567</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1308</v>
+        <v>-0.1555</v>
       </c>
       <c r="V2" t="n">
         <v>1.6363</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. ALEMAN ROMERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2855</v>
+        <v>3.5249</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6603</v>
+        <v>5.2852</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3748</v>
+        <v>-1.7603</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1873</v>
+        <v>3.3267</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1564</v>
+        <v>-0.8988</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.969</v>
+        <v>4.2256</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5566</v>
+        <v>6.9981</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4737</v>
+        <v>1.1293</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0829</v>
+        <v>5.8688</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3693</v>
+        <v>-3.6714</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3173</v>
+        <v>-2.0281</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.052</v>
+        <v>-1.6433</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1117</v>
+        <v>-3.7057</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7411</v>
+        <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4058</v>
+        <v>0.4328</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9572</v>
+        <v>1.0496</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5514</v>
+        <v>-0.6168</v>
       </c>
       <c r="V3" t="n">
-        <v>0.063</v>
+        <v>0.6919</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2583</v>
+        <v>0.9433</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1953</v>
+        <v>-0.2514</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALEMAN ROMERA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.627</v>
+        <v>1.8221</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6089</v>
+        <v>5.2461</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9819</v>
+        <v>-3.4241</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3267</v>
+        <v>1.1873</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8988</v>
+        <v>2.1564</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2256</v>
+        <v>-0.969</v>
       </c>
       <c r="J4" t="n">
-        <v>6.9981</v>
+        <v>3.5566</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1293</v>
+        <v>3.4737</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8688</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.6714</v>
+        <v>-2.3693</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0281</v>
+        <v>-1.3173</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6433</v>
+        <v>-1.052</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7057</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7793</v>
+        <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4651</v>
+        <v>0.9423</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6267</v>
+        <v>1.5429</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8384</v>
+        <v>-0.6006</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6919</v>
+        <v>0.063</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9433</v>
+        <v>1.2583</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2514</v>
+        <v>-1.1953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9334</v>
+        <v>1.4563</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6871</v>
+        <v>2.5225</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7537</v>
+        <v>-1.0662</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8403</v>
+        <v>-2.9878</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1489</v>
+        <v>1.3515</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3086</v>
+        <v>-4.3393</v>
       </c>
       <c r="J5" t="n">
-        <v>3.227</v>
+        <v>0.1323</v>
       </c>
       <c r="K5" t="n">
-        <v>2.439</v>
+        <v>2.5672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.788</v>
+        <v>-2.4349</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3867</v>
+        <v>-3.1201</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2901</v>
+        <v>-1.2157</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0966</v>
+        <v>-1.9044</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0382</v>
+        <v>-3.891</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>2.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>0.964</v>
+        <v>0.8285</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8133</v>
+        <v>1.2464</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1507</v>
+        <v>-0.4179</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.315</v>
+        <v>5.0979</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.315</v>
+        <v>5.0349</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4666</v>
+        <v>0.5707</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3358</v>
+        <v>1.546</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8692</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9878</v>
+        <v>0.8403</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3515</v>
+        <v>2.1489</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.3393</v>
+        <v>-1.3086</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1323</v>
+        <v>3.227</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5672</v>
+        <v>2.439</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.4349</v>
+        <v>0.788</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1201</v>
+        <v>-2.3867</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2157</v>
+        <v>-0.2901</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9044</v>
+        <v>-2.0966</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4823</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.891</v>
+        <v>-2.0382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4087</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1612</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0597</v>
+        <v>0.6721</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2209</v>
+        <v>-0.0709</v>
       </c>
       <c r="V6" t="n">
-        <v>5.0979</v>
+        <v>-0.315</v>
       </c>
       <c r="W6" t="n">
-        <v>5.0349</v>
+        <v>-0.315</v>
       </c>
       <c r="X6" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2828</v>
+        <v>-0.5349</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2843</v>
+        <v>1.192</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0015</v>
+        <v>-1.7269</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3427</v>
+        <v>-0.6331</v>
       </c>
       <c r="H7" t="n">
         <v>-2.186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8434</v>
+        <v>1.5529</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4028</v>
+        <v>1.8258</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4858</v>
+        <v>-0.9327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>2.7585</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9398</v>
+        <v>-2.4589</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7003</v>
+        <v>-1.2534</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7604</v>
+        <v>-1.2056</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4823</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5348</v>
+        <v>0.7844</v>
       </c>
       <c r="T7" t="n">
-        <v>1.639</v>
+        <v>1.2022</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1042</v>
+        <v>-0.4179</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0074</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2589</v>
+        <v>0.9433</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2514</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.449</v>
+        <v>-0.8224</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3764</v>
+        <v>-0.4193</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8254</v>
+        <v>-0.4031</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6331</v>
+        <v>-0.76</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.186</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5529</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8258</v>
+        <v>-0.6529</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9327</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7585</v>
+        <v>-0.6529</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4589</v>
+        <v>-0.1071</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2534</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2056</v>
+        <v>-0.023</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7793</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8702</v>
+        <v>-0.3948</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3866</v>
+        <v>0.0864</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5163</v>
+        <v>-0.4813</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3155</v>
+        <v>1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9433</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0429</v>
+        <v>-1.0668</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6152</v>
+        <v>-0.9698</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4277</v>
+        <v>-0.097</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.76</v>
+        <v>-1.3427</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-2.186</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.8434</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6529</v>
+        <v>-0.4028</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.4858</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6529</v>
+        <v>0.0829</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1071</v>
+        <v>-0.9398</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.7003</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.023</v>
+        <v>0.7604</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9264</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6153</v>
+        <v>0.7508</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1094</v>
+        <v>0.9535</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5059</v>
+        <v>-0.2027</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2589</v>
+        <v>1.0074</v>
       </c>
       <c r="W9" t="n">
         <v>1.2589</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2514</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2778</v>
+        <v>-2.0573</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2212</v>
+        <v>-1.0253</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0566</v>
+        <v>-1.032</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3683</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3542</v>
+        <v>-0.1337</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1094</v>
+        <v>0.0864</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2447</v>
+        <v>-0.2201</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6289</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3996</v>
+        <v>-6.9275</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0154</v>
+        <v>-1.7648</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.3842</v>
+        <v>-5.1626</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3731</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2323</v>
+        <v>0.7045</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8767</v>
+        <v>1.1273</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6444</v>
+        <v>-0.4228</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7766</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.269400000000001</v>
+        <v>0.2778999999999989</v>
       </c>
       <c r="E12" t="n">
-        <v>17.7106</v>
+        <v>18.2579</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.9799</v>
+        <v>-17.98</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.073599999999999</v>
+        <v>-3.0736</v>
       </c>
       <c r="H12" t="n">
         <v>-1.5376</v>
@@ -1366,10 +1366,10 @@
         <v>17.3132</v>
       </c>
       <c r="K12" t="n">
-        <v>9.864799999999999</v>
+        <v>9.864800000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.448400000000001</v>
+        <v>7.448399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-20.3868</v>
@@ -1390,13 +1390,13 @@
         <v>14.8229</v>
       </c>
       <c r="S12" t="n">
-        <v>4.570000000000001</v>
+        <v>5.1174</v>
       </c>
       <c r="T12" t="n">
-        <v>8.176600000000001</v>
+        <v>8.723500000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6063</v>
+        <v>-3.6065</v>
       </c>
       <c r="V12" t="n">
         <v>4.7194</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5214</v>
+        <v>4.1336</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6625</v>
+        <v>7.8584</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1411</v>
+        <v>-3.7248</v>
       </c>
       <c r="G13" t="n">
         <v>5.6741</v>
@@ -1468,13 +1468,13 @@
         <v>3.7057</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9734</v>
+        <v>-0.3613</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5484</v>
+        <v>0.7443</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5219</v>
+        <v>-1.1055</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2529</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9929</v>
+        <v>2.4155</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3294</v>
+        <v>2.4267</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3364</v>
+        <v>-0.0112</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0379</v>
+        <v>1.8098</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4526</v>
+        <v>0.3447</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4147</v>
+        <v>1.4651</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3956</v>
+        <v>4.637</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3956</v>
+        <v>1.4211</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.2159</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3577</v>
+        <v>-2.8272</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-1.0764</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4147</v>
+        <v>-1.7508</v>
       </c>
       <c r="P14" t="n">
         <v>0.9264</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9264</v>
+        <v>3.7057</v>
       </c>
       <c r="S14" t="n">
-        <v>0.713</v>
+        <v>-0.0684</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6193</v>
+        <v>0.5696</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.638</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3155</v>
+        <v>-0.2523</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>-0.0005</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0011</v>
+        <v>-0.2518</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.827</v>
+        <v>2.048</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5448</v>
+        <v>3.251</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7178</v>
+        <v>-1.2029</v>
       </c>
       <c r="G15" t="n">
         <v>1.4657</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7896</v>
+        <v>-0.5686</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6703</v>
+        <v>0.3765</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4599</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2578</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4562</v>
+        <v>1.8212</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7016</v>
+        <v>2.2314</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2454</v>
+        <v>-0.4103</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.52</v>
+        <v>0.0379</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4137</v>
+        <v>0.4526</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9337</v>
+        <v>-0.4147</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7854</v>
+        <v>1.3956</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5365</v>
+        <v>1.3956</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2488</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3054</v>
+        <v>-1.3577</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1228</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1826</v>
+        <v>-0.4147</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2234</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9583</v>
+        <v>0.5413</v>
       </c>
       <c r="T16" t="n">
-        <v>0.919</v>
+        <v>0.5214</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0393</v>
+        <v>0.0199</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5738</v>
+        <v>0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7766</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2027</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0852</v>
+        <v>1.2341</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6433</v>
+        <v>1.9167</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5581</v>
+        <v>-0.6826</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8098</v>
+        <v>-0.2709</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3447</v>
+        <v>-0.7608</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4651</v>
+        <v>0.4899</v>
       </c>
       <c r="J17" t="n">
-        <v>4.637</v>
+        <v>2.3043</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4211</v>
+        <v>0.2402</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2159</v>
+        <v>2.0641</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8272</v>
+        <v>-2.5752</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0764</v>
+        <v>-1.001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7508</v>
+        <v>-1.5743</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7057</v>
+        <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3987</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2139</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1849</v>
+        <v>-0.6355</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2523</v>
+        <v>-0.2512</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2518</v>
+        <v>-0.2512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7679</v>
+        <v>0.6282</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0146</v>
+        <v>3.0161</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2467</v>
+        <v>-2.3879</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2709</v>
+        <v>-0.52</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7608</v>
+        <v>0.4137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4899</v>
+        <v>-0.9337</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3043</v>
+        <v>1.7854</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2402</v>
+        <v>1.5365</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0641</v>
+        <v>0.2488</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5752</v>
+        <v>-2.3054</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.001</v>
+        <v>-1.1228</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5743</v>
+        <v>-1.1826</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8529</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5628</v>
+        <v>0.1303</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6367</v>
+        <v>0.2335</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1995</v>
+        <v>-0.1032</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2512</v>
+        <v>1.5738</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.7766</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2512</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4098</v>
+        <v>-0.3606</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0132</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3966</v>
+        <v>-0.3474</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2574</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1525</v>
+        <v>-0.1032</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2761</v>
+        <v>-1.0797</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4399</v>
+        <v>-0.342</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.7377</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4583</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1219</v>
+        <v>-0.9255</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.143</v>
+        <v>-0.0451</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9789</v>
+        <v>-0.8804</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2518</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1686</v>
+        <v>-1.8416</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5456</v>
+        <v>-0.4476</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.623</v>
+        <v>-1.394</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5851</v>
@@ -2170,13 +2170,13 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9366</v>
+        <v>-0.6096</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.143</v>
+        <v>-0.0451</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7936</v>
+        <v>-0.5646</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5733</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.64</v>
+        <v>-6.2312</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9042</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7358</v>
+        <v>-4.3269</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6955</v>
@@ -2248,13 +2248,13 @@
         <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1751</v>
+        <v>0.2338</v>
       </c>
       <c r="T23" t="n">
         <v>0.822</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9971</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7695</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2693000000000003</v>
+        <v>2.880700000000002</v>
       </c>
       <c r="E24" t="n">
         <v>17.9801</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.7107</v>
+        <v>-15.0993</v>
       </c>
       <c r="G24" t="n">
         <v>3.0735</v>
       </c>
       <c r="H24" t="n">
-        <v>1.537700000000001</v>
+        <v>1.5377</v>
       </c>
       <c r="I24" t="n">
         <v>1.5358</v>
@@ -2314,7 +2314,7 @@
         <v>-9.864799999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.448500000000001</v>
+        <v>-7.4485</v>
       </c>
       <c r="P24" t="n">
         <v>6.485000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>21.3078</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.5699</v>
+        <v>-1.9585</v>
       </c>
       <c r="T24" t="n">
-        <v>3.606400000000001</v>
+        <v>3.6065</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.176300000000001</v>
+        <v>-5.565</v>
       </c>
       <c r="V24" t="n">
         <v>-4.7195</v>
